--- a/Treinamento/IndexacaoFG/Arquivos/Relatório de Recusas 27.10.2025 a 02.11.2025.xlsx
+++ b/Treinamento/IndexacaoFG/Arquivos/Relatório de Recusas 27.10.2025 a 02.11.2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms.sharepoint.com/teams/BR0010-4356589/Shared Documents/BACK-OFFICE SME/Santander/2025/Relatório de Recusas/05. Maio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{933572E9-DC09-4588-9935-BAA6F135F1FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7542B29D-4A3F-40BB-92C4-6F8203FEC542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="2" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="27.10" sheetId="2" r:id="rId1"/>
@@ -21,6 +21,9 @@
     <sheet name="01.11" sheetId="6" r:id="rId6"/>
     <sheet name="02.11" sheetId="7" r:id="rId7"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'28.10'!$G$38:$G$43</definedName>
+  </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -42,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="144">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -293,12 +296,210 @@
   <si>
     <t>CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: Documento do veíc, Frente e lateral do mot, Traseira e lateral do mot, Traseira e lateral do pass, Chassi.</t>
   </si>
+  <si>
+    <t>LIMBO</t>
+  </si>
+  <si>
+    <t>EMERSON MENEZES DOS SANTOS CPF- 04835332547</t>
+  </si>
+  <si>
+    <t>Demais Motivos</t>
+  </si>
+  <si>
+    <t>Chassi irregular, favor corrigir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUIS FERNANDO DE MENEZES VIEIRA              </t>
+  </si>
+  <si>
+    <t>Divergência de bônus.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JEAN CLEI DA SILVA                           </t>
+  </si>
+  <si>
+    <t>Duplicidade;</t>
+  </si>
+  <si>
+    <t>Veículo em duplicidade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRISTIANE OLIVEIRA MORENO OLIANI             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCELO MARTINS LISBOA                       </t>
+  </si>
+  <si>
+    <t>Correção de bônus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NATANAEL ALMEIDA CAMPOS                      </t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 27.10.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAULO ROBERTO SOUZA DE MORAES                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSIANE MARIA DA SILVA                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEDRO ANTONIO ROCHA                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOAO FERREIRA GUIMARAES                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIGIA MARIA SILVA DE MORAES CARVALHO         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARLEIDE FREITAS LIMA SANTOS                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FERNANDA DINIZ DA SILVA                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROMERO CAMPOS DE SOUZA MOREIRA JUNIOR        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALYNE RIBEIRO LOPES SHINKAI                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLAUDIO DOS SANTOS                           </t>
+  </si>
+  <si>
+    <t>FRUSTRADO CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: Painel com carro ligado. Para-choque traseiro desalinhado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDER FALEIROS COSTA                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIRCEU TEIXEIRA GUIMARAES                    </t>
+  </si>
+  <si>
+    <t>RECUSA: FRUSTRADO PRAZO EXPIRADO * SEGURADO NÃO CORRIGIU OS PASSOS SOLICITADOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLAUDEMIR BUENO                              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">OLCIONE DOS SANTOS E SILVA                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RECUSA: FRUSTRADO PRAZO EXPIRADO * SEGURADO NÃO FEZ O ENVIO DAS DEMAIS FOTOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUSTAVO BECKER ROHDE                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">IZADORA MARIA CAMPOS RODRIGUES               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JULIANA FOWLER                               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARLOS ROBERTO DA SILVA                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANOEL NASCIMENTO LIBANIO DOS ANJOS          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Veículo em duplicidade com proposta </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DANIEL BARROS COSTA                          </t>
+  </si>
+  <si>
+    <t>Veículo informado é diferente do calculado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLEIDE TELES CARVALHO                        </t>
+  </si>
+  <si>
+    <t>Veículo em duplicidade com proposta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JACQUELINE MACHADO FERREIRA                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CESAR OSSAMU IDA                             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JUVENAL SIMOES DA COSTA                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDREA ALVES DOS SANTOS SALES                </t>
+  </si>
+  <si>
+    <t>Divergência de bônus.  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDREIA HONORATO GARCIA                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">APARECIDA COSTA                              </t>
+  </si>
+  <si>
+    <t>Divergência de bônus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAGRJ INSTALACOES ELETRICAS LTDA ME          </t>
+  </si>
+  <si>
+    <t>Bloqueio liberado pelo processo automático de vistoria prévia.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAULA SANT ANNA DE OLIVEIRA                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAURICIO CANSO CORDEIRO                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conforme consulta na central de bônus, identificamos que não
+há possibilidade efetuar a transferência de bônus para o(a) senhor
+(a) MAURICIO CANSO CORDEIRO , pois este não consta como condutor n
+a apólice anterior, conforme cópia enviada. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BENEDITO JOSE DE OLIVEIRA                    </t>
+  </si>
+  <si>
+    <t>CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: Documento, Frente e lateral do pass, Frente e lateral do mot, Traseira e lateral do mot, Traseira e lateral do pass, Motor, Painel, Chassi, Porta malas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AIRLENE PINHO VARGAS                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLAUDIA ELAINE PIRES DA SILVA                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUANA CRISTINA FERNANDES BATISTA             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMERCIAL FERREIRA LINCON LTDA EPP           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">THIAGO FAGUNDES DE FREITAS                   </t>
+  </si>
+  <si>
+    <t>28/10/25</t>
+  </si>
+  <si>
+    <t>29/10/25</t>
+  </si>
+  <si>
+    <t>BONIEK BRUNO JORGE SANTIAGO CPF 01777489318</t>
+  </si>
+  <si>
+    <t>A versão informada não corresponde ao chassi do veículo.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -335,6 +536,20 @@
       <color theme="1"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF414141"/>
+      <name val="Allianz Neo"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -350,7 +565,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -536,12 +751,45 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -591,7 +839,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -615,10 +862,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -652,10 +895,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -663,7 +902,44 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1048,25 +1324,25 @@
       <c r="B2" s="7">
         <v>45976</v>
       </c>
-      <c r="C2" s="27">
+      <c r="C2" s="26">
         <v>45957</v>
       </c>
-      <c r="D2" s="47">
+      <c r="D2" s="23">
         <v>134971230</v>
       </c>
       <c r="E2" s="18">
         <v>3450109971</v>
       </c>
-      <c r="F2" s="46" t="s">
+      <c r="F2" s="12" t="s">
         <v>10</v>
       </c>
       <c r="G2" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="49" t="s">
+      <c r="H2" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="48">
+      <c r="I2" s="43">
         <v>45954</v>
       </c>
     </row>
@@ -1077,25 +1353,25 @@
       <c r="B3" s="7">
         <v>45947</v>
       </c>
-      <c r="C3" s="27">
+      <c r="C3" s="26">
         <v>45957</v>
       </c>
-      <c r="D3" s="47">
+      <c r="D3" s="23">
         <v>134988741</v>
       </c>
       <c r="E3" s="18">
         <v>3450111423</v>
       </c>
-      <c r="F3" s="46" t="s">
+      <c r="F3" s="12" t="s">
         <v>13</v>
       </c>
       <c r="G3" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="49" t="s">
+      <c r="H3" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="48">
+      <c r="I3" s="43">
         <v>45947</v>
       </c>
     </row>
@@ -1106,25 +1382,25 @@
       <c r="B4" s="7">
         <v>45947</v>
       </c>
-      <c r="C4" s="27">
+      <c r="C4" s="26">
         <v>45957</v>
       </c>
-      <c r="D4" s="47">
+      <c r="D4" s="23">
         <v>134987327</v>
       </c>
       <c r="E4" s="18">
         <v>3450111170</v>
       </c>
-      <c r="F4" s="46" t="s">
+      <c r="F4" s="12" t="s">
         <v>16</v>
       </c>
       <c r="G4" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="49" t="s">
+      <c r="H4" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="48">
+      <c r="I4" s="43">
         <v>45947</v>
       </c>
     </row>
@@ -1135,25 +1411,25 @@
       <c r="B5" s="7">
         <v>45950</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="26">
         <v>45957</v>
       </c>
-      <c r="D5" s="47">
+      <c r="D5" s="23">
         <v>135019736</v>
       </c>
       <c r="E5" s="18">
         <v>3450113898</v>
       </c>
-      <c r="F5" s="46" t="s">
+      <c r="F5" s="12" t="s">
         <v>17</v>
       </c>
       <c r="G5" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="49" t="s">
+      <c r="H5" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="I5" s="48">
+      <c r="I5" s="43">
         <v>45950</v>
       </c>
     </row>
@@ -1164,25 +1440,25 @@
       <c r="B6" s="7">
         <v>45950</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="26">
         <v>45957</v>
       </c>
-      <c r="D6" s="47">
+      <c r="D6" s="23">
         <v>135015163</v>
       </c>
       <c r="E6" s="18">
         <v>3450113480</v>
       </c>
-      <c r="F6" s="46" t="s">
+      <c r="F6" s="12" t="s">
         <v>20</v>
       </c>
       <c r="G6" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="50" t="s">
+      <c r="H6" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="I6" s="48">
+      <c r="I6" s="43">
         <v>45950</v>
       </c>
     </row>
@@ -1193,25 +1469,25 @@
       <c r="B7" s="7">
         <v>45951</v>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="26">
         <v>45957</v>
       </c>
-      <c r="D7" s="47">
+      <c r="D7" s="23">
         <v>135026243</v>
       </c>
       <c r="E7" s="18">
         <v>3450114140</v>
       </c>
-      <c r="F7" s="46" t="s">
+      <c r="F7" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="G7" s="25" t="s">
+      <c r="G7" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="H7" s="51" t="s">
+      <c r="H7" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="I7" s="48">
+      <c r="I7" s="43">
         <v>45951</v>
       </c>
     </row>
@@ -1222,25 +1498,25 @@
       <c r="B8" s="7">
         <v>45971</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="26">
         <v>45957</v>
       </c>
-      <c r="D8" s="47">
+      <c r="D8" s="23">
         <v>135046529</v>
       </c>
       <c r="E8" s="18">
         <v>3450115999</v>
       </c>
-      <c r="F8" s="46" t="s">
+      <c r="F8" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="G8" s="25" t="s">
+      <c r="G8" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="H8" s="51" t="s">
+      <c r="H8" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="I8" s="48">
+      <c r="I8" s="43">
         <v>45954</v>
       </c>
     </row>
@@ -1251,25 +1527,25 @@
       <c r="B9" s="7">
         <v>45952</v>
       </c>
-      <c r="C9" s="27">
+      <c r="C9" s="26">
         <v>45957</v>
       </c>
-      <c r="D9" s="47">
+      <c r="D9" s="23">
         <v>135048698</v>
       </c>
       <c r="E9" s="18">
         <v>3450116252</v>
       </c>
-      <c r="F9" s="46" t="s">
+      <c r="F9" s="12" t="s">
         <v>26</v>
       </c>
       <c r="G9" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="H9" s="52" t="s">
+      <c r="H9" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="I9" s="48">
+      <c r="I9" s="43">
         <v>45952</v>
       </c>
     </row>
@@ -1280,25 +1556,25 @@
       <c r="B10" s="7">
         <v>45952</v>
       </c>
-      <c r="C10" s="27">
+      <c r="C10" s="26">
         <v>45957</v>
       </c>
-      <c r="D10" s="47">
+      <c r="D10" s="23">
         <v>135048914</v>
       </c>
       <c r="E10" s="18">
         <v>3450116318</v>
       </c>
-      <c r="F10" s="46" t="s">
+      <c r="F10" s="12" t="s">
         <v>28</v>
       </c>
       <c r="G10" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="H10" s="49" t="s">
+      <c r="H10" s="44" t="s">
         <v>29</v>
       </c>
-      <c r="I10" s="48">
+      <c r="I10" s="43">
         <v>45952</v>
       </c>
     </row>
@@ -1309,25 +1585,25 @@
       <c r="B11" s="7">
         <v>45952</v>
       </c>
-      <c r="C11" s="27">
+      <c r="C11" s="26">
         <v>45957</v>
       </c>
-      <c r="D11" s="47">
+      <c r="D11" s="23">
         <v>135050384</v>
       </c>
       <c r="E11" s="18">
         <v>3450116549</v>
       </c>
-      <c r="F11" s="46" t="s">
+      <c r="F11" s="12" t="s">
         <v>30</v>
       </c>
       <c r="G11" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="H11" s="49" t="s">
+      <c r="H11" s="44" t="s">
         <v>31</v>
       </c>
-      <c r="I11" s="48">
+      <c r="I11" s="43">
         <v>45952</v>
       </c>
     </row>
@@ -1338,25 +1614,25 @@
       <c r="B12" s="7">
         <v>45952</v>
       </c>
-      <c r="C12" s="27">
+      <c r="C12" s="26">
         <v>45957</v>
       </c>
-      <c r="D12" s="47">
+      <c r="D12" s="23">
         <v>135049543</v>
       </c>
       <c r="E12" s="18">
         <v>3450116406</v>
       </c>
-      <c r="F12" s="46" t="s">
+      <c r="F12" s="12" t="s">
         <v>32</v>
       </c>
       <c r="G12" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="H12" s="49" t="s">
+      <c r="H12" s="44" t="s">
         <v>33</v>
       </c>
-      <c r="I12" s="48">
+      <c r="I12" s="43">
         <v>45952</v>
       </c>
     </row>
@@ -1367,25 +1643,25 @@
       <c r="B13" s="7">
         <v>45952</v>
       </c>
-      <c r="C13" s="27">
+      <c r="C13" s="26">
         <v>45957</v>
       </c>
-      <c r="D13" s="47">
+      <c r="D13" s="23">
         <v>135050051</v>
       </c>
       <c r="E13" s="18">
         <v>3450116494</v>
       </c>
-      <c r="F13" s="46" t="s">
+      <c r="F13" s="12" t="s">
         <v>34</v>
       </c>
       <c r="G13" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="H13" s="49" t="s">
+      <c r="H13" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="I13" s="48">
+      <c r="I13" s="43">
         <v>45952</v>
       </c>
     </row>
@@ -1396,25 +1672,25 @@
       <c r="B14" s="7">
         <v>45952</v>
       </c>
-      <c r="C14" s="27">
+      <c r="C14" s="26">
         <v>45957</v>
       </c>
-      <c r="D14" s="47">
+      <c r="D14" s="23">
         <v>135044777</v>
       </c>
       <c r="E14" s="18">
         <v>3450115889</v>
       </c>
-      <c r="F14" s="46" t="s">
+      <c r="F14" s="12" t="s">
         <v>37</v>
       </c>
       <c r="G14" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="H14" s="49" t="s">
+      <c r="H14" s="44" t="s">
         <v>38</v>
       </c>
-      <c r="I14" s="48">
+      <c r="I14" s="43">
         <v>45952</v>
       </c>
     </row>
@@ -1425,25 +1701,25 @@
       <c r="B15" s="7">
         <v>45952</v>
       </c>
-      <c r="C15" s="27">
+      <c r="C15" s="26">
         <v>45957</v>
       </c>
-      <c r="D15" s="47">
+      <c r="D15" s="23">
         <v>135052121</v>
       </c>
       <c r="E15" s="18">
         <v>3450116802</v>
       </c>
-      <c r="F15" s="46" t="s">
+      <c r="F15" s="12" t="s">
         <v>39</v>
       </c>
       <c r="G15" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="H15" s="49" t="s">
+      <c r="H15" s="44" t="s">
         <v>40</v>
       </c>
-      <c r="I15" s="48">
+      <c r="I15" s="43">
         <v>45952</v>
       </c>
     </row>
@@ -1454,25 +1730,25 @@
       <c r="B16" s="7">
         <v>45952</v>
       </c>
-      <c r="C16" s="27">
+      <c r="C16" s="26">
         <v>45957</v>
       </c>
-      <c r="D16" s="47">
+      <c r="D16" s="23">
         <v>135060115</v>
       </c>
       <c r="E16" s="18">
         <v>3450117737</v>
       </c>
-      <c r="F16" s="46" t="s">
+      <c r="F16" s="12" t="s">
         <v>41</v>
       </c>
       <c r="G16" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="H16" s="49" t="s">
+      <c r="H16" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="I16" s="48">
+      <c r="I16" s="43">
         <v>45952</v>
       </c>
     </row>
@@ -1483,25 +1759,25 @@
       <c r="B17" s="7">
         <v>45955</v>
       </c>
-      <c r="C17" s="27">
+      <c r="C17" s="26">
         <v>45957</v>
       </c>
-      <c r="D17" s="47">
+      <c r="D17" s="23">
         <v>135048549</v>
       </c>
       <c r="E17" s="18">
         <v>3450116230</v>
       </c>
-      <c r="F17" s="46" t="s">
+      <c r="F17" s="12" t="s">
         <v>43</v>
       </c>
       <c r="G17" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="H17" s="53" t="s">
+      <c r="H17" s="44" t="s">
         <v>45</v>
       </c>
-      <c r="I17" s="48">
+      <c r="I17" s="43">
         <v>45957</v>
       </c>
     </row>
@@ -1512,25 +1788,25 @@
       <c r="B18" s="7">
         <v>45952</v>
       </c>
-      <c r="C18" s="27">
+      <c r="C18" s="26">
         <v>45957</v>
       </c>
-      <c r="D18" s="47">
+      <c r="D18" s="23">
         <v>135056897</v>
       </c>
       <c r="E18" s="18">
         <v>3450117242</v>
       </c>
-      <c r="F18" s="46" t="s">
+      <c r="F18" s="12" t="s">
         <v>46</v>
       </c>
       <c r="G18" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="H18" s="49" t="s">
+      <c r="H18" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="I18" s="48">
+      <c r="I18" s="43">
         <v>45952</v>
       </c>
     </row>
@@ -1541,25 +1817,25 @@
       <c r="B19" s="7">
         <v>45954</v>
       </c>
-      <c r="C19" s="27">
+      <c r="C19" s="26">
         <v>45957</v>
       </c>
-      <c r="D19" s="47">
+      <c r="D19" s="23">
         <v>135083023</v>
       </c>
       <c r="E19" s="18">
         <v>3450119266</v>
       </c>
-      <c r="F19" s="46" t="s">
+      <c r="F19" s="12" t="s">
         <v>47</v>
       </c>
       <c r="G19" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="H19" s="49" t="s">
+      <c r="H19" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="I19" s="48">
+      <c r="I19" s="43">
         <v>45954</v>
       </c>
     </row>
@@ -1570,25 +1846,25 @@
       <c r="B20" s="7">
         <v>45952</v>
       </c>
-      <c r="C20" s="27">
+      <c r="C20" s="26">
         <v>45957</v>
       </c>
-      <c r="D20" s="47">
+      <c r="D20" s="23">
         <v>135058343</v>
       </c>
       <c r="E20" s="18">
         <v>3450117484</v>
       </c>
-      <c r="F20" s="46" t="s">
+      <c r="F20" s="12" t="s">
         <v>48</v>
       </c>
       <c r="G20" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="H20" s="49" t="s">
+      <c r="H20" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="I20" s="48">
+      <c r="I20" s="43">
         <v>45954</v>
       </c>
     </row>
@@ -1599,25 +1875,25 @@
       <c r="B21" s="7">
         <v>45958</v>
       </c>
-      <c r="C21" s="27">
+      <c r="C21" s="26">
         <v>45957</v>
       </c>
-      <c r="D21" s="47">
+      <c r="D21" s="23">
         <v>135090745</v>
       </c>
       <c r="E21" s="18">
         <v>3450119849</v>
       </c>
-      <c r="F21" s="46" t="s">
+      <c r="F21" s="12" t="s">
         <v>49</v>
       </c>
       <c r="G21" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="H21" s="49" t="s">
+      <c r="H21" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="I21" s="48">
+      <c r="I21" s="43">
         <v>45954</v>
       </c>
     </row>
@@ -1628,25 +1904,25 @@
       <c r="B22" s="7">
         <v>45952</v>
       </c>
-      <c r="C22" s="27">
+      <c r="C22" s="26">
         <v>45957</v>
       </c>
-      <c r="D22" s="47">
+      <c r="D22" s="23">
         <v>135052917</v>
       </c>
       <c r="E22" s="18">
         <v>3450116846</v>
       </c>
-      <c r="F22" s="46" t="s">
+      <c r="F22" s="12" t="s">
         <v>50</v>
       </c>
       <c r="G22" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="H22" s="49" t="s">
+      <c r="H22" s="44" t="s">
         <v>51</v>
       </c>
-      <c r="I22" s="48">
+      <c r="I22" s="43">
         <v>45952</v>
       </c>
     </row>
@@ -1657,25 +1933,25 @@
       <c r="B23" s="7">
         <v>45954</v>
       </c>
-      <c r="C23" s="27">
+      <c r="C23" s="26">
         <v>45957</v>
       </c>
-      <c r="D23" s="47">
+      <c r="D23" s="23">
         <v>135094626</v>
       </c>
       <c r="E23" s="18">
         <v>3450120278</v>
       </c>
-      <c r="F23" s="46" t="s">
+      <c r="F23" s="12" t="s">
         <v>52</v>
       </c>
       <c r="G23" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="H23" s="49" t="s">
+      <c r="H23" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="I23" s="48">
+      <c r="I23" s="43">
         <v>45954</v>
       </c>
     </row>
@@ -1686,25 +1962,25 @@
       <c r="B24" s="7">
         <v>45944</v>
       </c>
-      <c r="C24" s="27">
+      <c r="C24" s="26">
         <v>45957</v>
       </c>
-      <c r="D24" s="47">
+      <c r="D24" s="23">
         <v>134918888</v>
       </c>
       <c r="E24" s="18">
         <v>3450106913</v>
       </c>
-      <c r="F24" s="46" t="s">
+      <c r="F24" s="12" t="s">
         <v>53</v>
       </c>
       <c r="G24" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="H24" s="53" t="s">
+      <c r="H24" s="44" t="s">
         <v>54</v>
       </c>
-      <c r="I24" s="48">
+      <c r="I24" s="43">
         <v>45957</v>
       </c>
     </row>
@@ -1715,25 +1991,25 @@
       <c r="B25" s="7">
         <v>45952</v>
       </c>
-      <c r="C25" s="27">
+      <c r="C25" s="26">
         <v>45957</v>
       </c>
-      <c r="D25" s="47">
+      <c r="D25" s="23">
         <v>135054365</v>
       </c>
       <c r="E25" s="18">
         <v>3450116945</v>
       </c>
-      <c r="F25" s="46" t="s">
+      <c r="F25" s="12" t="s">
         <v>55</v>
       </c>
       <c r="G25" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="H25" s="49" t="s">
+      <c r="H25" s="44" t="s">
         <v>56</v>
       </c>
-      <c r="I25" s="48">
+      <c r="I25" s="43">
         <v>45952</v>
       </c>
     </row>
@@ -1744,25 +2020,25 @@
       <c r="B26" s="7">
         <v>45971</v>
       </c>
-      <c r="C26" s="27">
+      <c r="C26" s="26">
         <v>45957</v>
       </c>
-      <c r="D26" s="47">
+      <c r="D26" s="23">
         <v>135028570</v>
       </c>
       <c r="E26" s="18">
         <v>3450114448</v>
       </c>
-      <c r="F26" s="46" t="s">
+      <c r="F26" s="12" t="s">
         <v>57</v>
       </c>
       <c r="G26" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="H26" s="49" t="s">
+      <c r="H26" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I26" s="48">
+      <c r="I26" s="43">
         <v>45954</v>
       </c>
     </row>
@@ -1773,25 +2049,25 @@
       <c r="B27" s="7">
         <v>45944</v>
       </c>
-      <c r="C27" s="27">
+      <c r="C27" s="26">
         <v>45957</v>
       </c>
-      <c r="D27" s="47">
+      <c r="D27" s="23">
         <v>134932306</v>
       </c>
       <c r="E27" s="18">
         <v>3450107738</v>
       </c>
-      <c r="F27" s="46" t="s">
+      <c r="F27" s="12" t="s">
         <v>58</v>
       </c>
       <c r="G27" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="H27" s="53" t="s">
+      <c r="H27" s="44" t="s">
         <v>59</v>
       </c>
-      <c r="I27" s="48">
+      <c r="I27" s="43">
         <v>45947</v>
       </c>
     </row>
@@ -1802,25 +2078,25 @@
       <c r="B28" s="7">
         <v>45952</v>
       </c>
-      <c r="C28" s="27">
+      <c r="C28" s="26">
         <v>45957</v>
       </c>
-      <c r="D28" s="47">
+      <c r="D28" s="23">
         <v>135050900</v>
       </c>
       <c r="E28" s="18">
         <v>3450116626</v>
       </c>
-      <c r="F28" s="46" t="s">
+      <c r="F28" s="12" t="s">
         <v>60</v>
       </c>
       <c r="G28" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="H28" s="49" t="s">
+      <c r="H28" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="I28" s="48">
+      <c r="I28" s="43">
         <v>45952</v>
       </c>
     </row>
@@ -1831,25 +2107,25 @@
       <c r="B29" s="7">
         <v>45946</v>
       </c>
-      <c r="C29" s="27">
+      <c r="C29" s="26">
         <v>45957</v>
       </c>
-      <c r="D29" s="47">
+      <c r="D29" s="23">
         <v>134963451</v>
       </c>
       <c r="E29" s="18">
         <v>3450109366</v>
       </c>
-      <c r="F29" s="46" t="s">
+      <c r="F29" s="12" t="s">
         <v>61</v>
       </c>
       <c r="G29" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="H29" s="49" t="s">
+      <c r="H29" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="I29" s="48">
+      <c r="I29" s="43">
         <v>45954</v>
       </c>
     </row>
@@ -1860,25 +2136,25 @@
       <c r="B30" s="7">
         <v>45977</v>
       </c>
-      <c r="C30" s="27">
+      <c r="C30" s="26">
         <v>45957</v>
       </c>
-      <c r="D30" s="47">
+      <c r="D30" s="23">
         <v>134994340</v>
       </c>
       <c r="E30" s="18">
         <v>3450111918</v>
       </c>
-      <c r="F30" s="46" t="s">
+      <c r="F30" s="12" t="s">
         <v>62</v>
       </c>
       <c r="G30" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="H30" s="49" t="s">
+      <c r="H30" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="I30" s="48">
+      <c r="I30" s="43">
         <v>45954</v>
       </c>
     </row>
@@ -1889,25 +2165,25 @@
       <c r="B31" s="7">
         <v>45971</v>
       </c>
-      <c r="C31" s="27">
+      <c r="C31" s="26">
         <v>45957</v>
       </c>
-      <c r="D31" s="47">
+      <c r="D31" s="23">
         <v>134988980</v>
       </c>
       <c r="E31" s="18">
         <v>3450111445</v>
       </c>
-      <c r="F31" s="46" t="s">
+      <c r="F31" s="12" t="s">
         <v>63</v>
       </c>
       <c r="G31" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="H31" s="53" t="s">
+      <c r="H31" s="44" t="s">
         <v>64</v>
       </c>
-      <c r="I31" s="48">
+      <c r="I31" s="43">
         <v>45952</v>
       </c>
     </row>
@@ -1918,25 +2194,25 @@
       <c r="B32" s="7">
         <v>45951</v>
       </c>
-      <c r="C32" s="27">
+      <c r="C32" s="26">
         <v>45957</v>
       </c>
-      <c r="D32" s="47">
+      <c r="D32" s="23">
         <v>135033815</v>
       </c>
       <c r="E32" s="18">
         <v>3450114976</v>
       </c>
-      <c r="F32" s="46" t="s">
+      <c r="F32" s="12" t="s">
         <v>65</v>
       </c>
       <c r="G32" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="H32" s="49" t="s">
+      <c r="H32" s="44" t="s">
         <v>66</v>
       </c>
-      <c r="I32" s="48">
+      <c r="I32" s="43">
         <v>45951</v>
       </c>
     </row>
@@ -1947,25 +2223,25 @@
       <c r="B33" s="7">
         <v>45952</v>
       </c>
-      <c r="C33" s="27">
+      <c r="C33" s="26">
         <v>45957</v>
       </c>
-      <c r="D33" s="47">
+      <c r="D33" s="23">
         <v>135054537</v>
       </c>
       <c r="E33" s="18">
         <v>3450116956</v>
       </c>
-      <c r="F33" s="46" t="s">
+      <c r="F33" s="12" t="s">
         <v>67</v>
       </c>
       <c r="G33" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="H33" s="49" t="s">
+      <c r="H33" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="I33" s="48">
+      <c r="I33" s="43">
         <v>45952</v>
       </c>
     </row>
@@ -1976,25 +2252,25 @@
       <c r="B34" s="7">
         <v>45952</v>
       </c>
-      <c r="C34" s="27">
+      <c r="C34" s="26">
         <v>45957</v>
       </c>
-      <c r="D34" s="47">
+      <c r="D34" s="23">
         <v>135055563</v>
       </c>
       <c r="E34" s="18">
         <v>3450117055</v>
       </c>
-      <c r="F34" s="46" t="s">
+      <c r="F34" s="12" t="s">
         <v>68</v>
       </c>
       <c r="G34" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="H34" s="49" t="s">
+      <c r="H34" s="44" t="s">
         <v>69</v>
       </c>
-      <c r="I34" s="48">
+      <c r="I34" s="43">
         <v>45952</v>
       </c>
     </row>
@@ -2005,25 +2281,25 @@
       <c r="B35" s="7">
         <v>45947</v>
       </c>
-      <c r="C35" s="27">
+      <c r="C35" s="26">
         <v>45957</v>
       </c>
-      <c r="D35" s="47">
+      <c r="D35" s="23">
         <v>134983887</v>
       </c>
       <c r="E35" s="18">
         <v>3450110785</v>
       </c>
-      <c r="F35" s="46" t="s">
+      <c r="F35" s="12" t="s">
         <v>70</v>
       </c>
       <c r="G35" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="H35" s="49" t="s">
+      <c r="H35" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="I35" s="48">
+      <c r="I35" s="43">
         <v>45947</v>
       </c>
     </row>
@@ -2034,25 +2310,25 @@
       <c r="B36" s="7">
         <v>45947</v>
       </c>
-      <c r="C36" s="27">
+      <c r="C36" s="26">
         <v>45957</v>
       </c>
-      <c r="D36" s="47">
+      <c r="D36" s="23">
         <v>134986277</v>
       </c>
       <c r="E36" s="18">
         <v>3450110983</v>
       </c>
-      <c r="F36" s="46" t="s">
+      <c r="F36" s="12" t="s">
         <v>71</v>
       </c>
       <c r="G36" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="H36" s="49" t="s">
+      <c r="H36" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="I36" s="48">
+      <c r="I36" s="43">
         <v>45947</v>
       </c>
     </row>
@@ -2063,25 +2339,25 @@
       <c r="B37" s="7">
         <v>45947</v>
       </c>
-      <c r="C37" s="27">
+      <c r="C37" s="26">
         <v>45957</v>
       </c>
-      <c r="D37" s="47">
+      <c r="D37" s="23">
         <v>134995666</v>
       </c>
       <c r="E37" s="18">
         <v>3450112017</v>
       </c>
-      <c r="F37" s="46" t="s">
+      <c r="F37" s="12" t="s">
         <v>72</v>
       </c>
       <c r="G37" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="H37" s="49" t="s">
+      <c r="H37" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="I37" s="48">
+      <c r="I37" s="43">
         <v>45947</v>
       </c>
     </row>
@@ -2092,25 +2368,25 @@
       <c r="B38" s="7">
         <v>45947</v>
       </c>
-      <c r="C38" s="27">
+      <c r="C38" s="26">
         <v>45957</v>
       </c>
-      <c r="D38" s="47">
+      <c r="D38" s="23">
         <v>134996771</v>
       </c>
       <c r="E38" s="18">
         <v>3450112171</v>
       </c>
-      <c r="F38" s="46" t="s">
+      <c r="F38" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="G38" s="23" t="s">
+      <c r="G38" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="H38" s="49" t="s">
+      <c r="H38" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="I38" s="48">
+      <c r="I38" s="43">
         <v>45947</v>
       </c>
     </row>
@@ -2121,25 +2397,25 @@
       <c r="B39" s="7">
         <v>45947</v>
       </c>
-      <c r="C39" s="27">
+      <c r="C39" s="26">
         <v>45957</v>
       </c>
-      <c r="D39" s="47">
+      <c r="D39" s="23">
         <v>134999685</v>
       </c>
       <c r="E39" s="18">
         <v>3450112479</v>
       </c>
-      <c r="F39" s="46" t="s">
+      <c r="F39" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="G39" s="23" t="s">
+      <c r="G39" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="H39" s="49" t="s">
+      <c r="H39" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="I39" s="48">
+      <c r="I39" s="43">
         <v>45947</v>
       </c>
     </row>
@@ -2150,25 +2426,25 @@
       <c r="B40" s="7">
         <v>45952</v>
       </c>
-      <c r="C40" s="27">
+      <c r="C40" s="26">
         <v>45957</v>
       </c>
-      <c r="D40" s="47">
+      <c r="D40" s="23">
         <v>135051340</v>
       </c>
       <c r="E40" s="18">
         <v>3450116670</v>
       </c>
-      <c r="F40" s="46" t="s">
+      <c r="F40" s="12" t="s">
         <v>75</v>
       </c>
       <c r="G40" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="H40" s="53" t="s">
+      <c r="H40" s="44" t="s">
         <v>76</v>
       </c>
-      <c r="I40" s="48">
+      <c r="I40" s="43">
         <v>45952</v>
       </c>
     </row>
@@ -2179,25 +2455,25 @@
       <c r="B41" s="7">
         <v>45953</v>
       </c>
-      <c r="C41" s="27">
+      <c r="C41" s="26">
         <v>45957</v>
       </c>
-      <c r="D41" s="47">
+      <c r="D41" s="23">
         <v>135073583</v>
       </c>
       <c r="E41" s="18">
         <v>3450118573</v>
       </c>
-      <c r="F41" s="46" t="s">
+      <c r="F41" s="12" t="s">
         <v>77</v>
       </c>
       <c r="G41" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="H41" s="49" t="s">
+      <c r="H41" s="44" t="s">
         <v>78</v>
       </c>
-      <c r="I41" s="48">
+      <c r="I41" s="43">
         <v>45953</v>
       </c>
     </row>
@@ -2205,8 +2481,8 @@
       <c r="A42" s="6"/>
       <c r="B42" s="8"/>
       <c r="C42" s="7"/>
-      <c r="D42" s="22"/>
-      <c r="E42" s="22"/>
+      <c r="D42" s="21"/>
+      <c r="E42" s="21"/>
       <c r="F42" s="15"/>
       <c r="G42" s="6"/>
       <c r="H42" s="9"/>
@@ -2371,7 +2647,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFA17127-7620-4DD9-9061-6C654E2EC5C2}">
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -2379,7 +2655,7 @@
     <col min="3" max="3" width="21.5703125" customWidth="1"/>
     <col min="4" max="4" width="27.7109375" style="17" customWidth="1"/>
     <col min="5" max="5" width="18.5703125" customWidth="1"/>
-    <col min="6" max="6" width="31.5703125" customWidth="1"/>
+    <col min="6" max="6" width="51.42578125" customWidth="1"/>
     <col min="7" max="7" width="19.7109375" customWidth="1"/>
     <col min="8" max="8" width="24" customWidth="1"/>
     <col min="9" max="9" width="22.7109375" style="16" customWidth="1"/>
@@ -2415,642 +2691,1241 @@
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="26"/>
+      <c r="A2" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="43">
+        <v>45957</v>
+      </c>
+      <c r="C2" s="43">
+        <v>45958</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="E2" s="18">
+        <v>3450121950</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="G2" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="H2" s="49" t="s">
+        <v>82</v>
+      </c>
+      <c r="I2" s="43"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="26"/>
+      <c r="A3" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="43">
+        <v>45949</v>
+      </c>
+      <c r="C3" s="43">
+        <v>45958</v>
+      </c>
+      <c r="D3" s="51">
+        <v>134942483</v>
+      </c>
+      <c r="E3" s="18">
+        <v>3450108080</v>
+      </c>
+      <c r="F3" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="G3" s="48" t="s">
+        <v>44</v>
+      </c>
+      <c r="H3" s="49" t="s">
+        <v>84</v>
+      </c>
+      <c r="I3" s="43">
+        <v>45958</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="26"/>
+      <c r="A4" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="43">
+        <v>45945</v>
+      </c>
+      <c r="C4" s="43">
+        <v>45958</v>
+      </c>
+      <c r="D4" s="51">
+        <v>134954593</v>
+      </c>
+      <c r="E4" s="18">
+        <v>3450108959</v>
+      </c>
+      <c r="F4" s="50" t="s">
+        <v>85</v>
+      </c>
+      <c r="G4" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="H4" s="49" t="s">
+        <v>87</v>
+      </c>
+      <c r="I4" s="43">
+        <v>45958</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="26"/>
+      <c r="A5" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="43">
+        <v>45946</v>
+      </c>
+      <c r="C5" s="43">
+        <v>45958</v>
+      </c>
+      <c r="D5" s="51">
+        <v>134954580</v>
+      </c>
+      <c r="E5" s="18">
+        <v>3450108948</v>
+      </c>
+      <c r="F5" s="50" t="s">
+        <v>88</v>
+      </c>
+      <c r="G5" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="H5" s="49" t="s">
+        <v>87</v>
+      </c>
+      <c r="I5" s="43">
+        <v>45958</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="26"/>
+      <c r="A6" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="43">
+        <v>45961</v>
+      </c>
+      <c r="C6" s="43">
+        <v>45958</v>
+      </c>
+      <c r="D6" s="51">
+        <v>134953873</v>
+      </c>
+      <c r="E6" s="18">
+        <v>3450108882</v>
+      </c>
+      <c r="F6" s="50" t="s">
+        <v>89</v>
+      </c>
+      <c r="G6" s="48" t="s">
+        <v>44</v>
+      </c>
+      <c r="H6" s="49" t="s">
+        <v>90</v>
+      </c>
+      <c r="I6" s="43">
+        <v>45958</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="30"/>
-      <c r="I7" s="26"/>
+      <c r="A7" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="43">
+        <v>45946</v>
+      </c>
+      <c r="C7" s="43">
+        <v>45958</v>
+      </c>
+      <c r="D7" s="51">
+        <v>134976368</v>
+      </c>
+      <c r="E7" s="18">
+        <v>3450110422</v>
+      </c>
+      <c r="F7" s="50" t="s">
+        <v>91</v>
+      </c>
+      <c r="G7" s="48" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" s="57" t="s">
+        <v>92</v>
+      </c>
+      <c r="I7" s="43">
+        <v>45957</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="26"/>
+      <c r="A8" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="43">
+        <v>45947</v>
+      </c>
+      <c r="C8" s="43">
+        <v>45958</v>
+      </c>
+      <c r="D8" s="51">
+        <v>135000174</v>
+      </c>
+      <c r="E8" s="18">
+        <v>3450112545</v>
+      </c>
+      <c r="F8" s="50" t="s">
+        <v>93</v>
+      </c>
+      <c r="G8" s="48" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="57" t="s">
+        <v>92</v>
+      </c>
+      <c r="I8" s="43">
+        <v>45957</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="24"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="26"/>
+      <c r="A9" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="43">
+        <v>45945</v>
+      </c>
+      <c r="C9" s="43">
+        <v>45958</v>
+      </c>
+      <c r="D9" s="51">
+        <v>134949643</v>
+      </c>
+      <c r="E9" s="18">
+        <v>3450108596</v>
+      </c>
+      <c r="F9" s="50" t="s">
+        <v>94</v>
+      </c>
+      <c r="G9" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="H9" s="49" t="s">
+        <v>87</v>
+      </c>
+      <c r="I9" s="43">
+        <v>45958</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="26"/>
+      <c r="A10" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="43">
+        <v>45950</v>
+      </c>
+      <c r="C10" s="43">
+        <v>45958</v>
+      </c>
+      <c r="D10" s="51">
+        <v>135009736</v>
+      </c>
+      <c r="E10" s="18">
+        <v>3450113007</v>
+      </c>
+      <c r="F10" s="50" t="s">
+        <v>95</v>
+      </c>
+      <c r="G10" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10" s="49" t="s">
+        <v>15</v>
+      </c>
+      <c r="I10" s="43">
+        <v>45950</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="26"/>
+      <c r="A11" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="43">
+        <v>45950</v>
+      </c>
+      <c r="C11" s="43">
+        <v>45958</v>
+      </c>
+      <c r="D11" s="51">
+        <v>135011662</v>
+      </c>
+      <c r="E11" s="18">
+        <v>3450113183</v>
+      </c>
+      <c r="F11" s="50" t="s">
+        <v>96</v>
+      </c>
+      <c r="G11" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11" s="49" t="s">
+        <v>15</v>
+      </c>
+      <c r="I11" s="43">
+        <v>45950</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="26"/>
+      <c r="A12" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="43">
+        <v>45950</v>
+      </c>
+      <c r="C12" s="43">
+        <v>45958</v>
+      </c>
+      <c r="D12" s="51">
+        <v>135016864</v>
+      </c>
+      <c r="E12" s="18">
+        <v>3450113579</v>
+      </c>
+      <c r="F12" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="G12" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" s="49" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" s="43">
+        <v>45950</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="26"/>
+      <c r="A13" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="43">
+        <v>45952</v>
+      </c>
+      <c r="C13" s="43">
+        <v>45958</v>
+      </c>
+      <c r="D13" s="51">
+        <v>135040056</v>
+      </c>
+      <c r="E13" s="18">
+        <v>3450115669</v>
+      </c>
+      <c r="F13" s="50" t="s">
+        <v>98</v>
+      </c>
+      <c r="G13" s="48" t="s">
+        <v>11</v>
+      </c>
+      <c r="H13" s="49" t="s">
+        <v>12</v>
+      </c>
+      <c r="I13" s="43">
+        <v>45957</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="26"/>
+      <c r="A14" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="43">
+        <v>45951</v>
+      </c>
+      <c r="C14" s="43">
+        <v>45958</v>
+      </c>
+      <c r="D14" s="51">
+        <v>135040123</v>
+      </c>
+      <c r="E14" s="18">
+        <v>3450115670</v>
+      </c>
+      <c r="F14" s="50" t="s">
+        <v>99</v>
+      </c>
+      <c r="G14" s="48" t="s">
+        <v>11</v>
+      </c>
+      <c r="H14" s="57" t="s">
+        <v>92</v>
+      </c>
+      <c r="I14" s="43">
+        <v>45957</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="26"/>
+      <c r="A15" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="43">
+        <v>45945</v>
+      </c>
+      <c r="C15" s="43">
+        <v>45958</v>
+      </c>
+      <c r="D15" s="51">
+        <v>134945073</v>
+      </c>
+      <c r="E15" s="18">
+        <v>3450108321</v>
+      </c>
+      <c r="F15" s="50" t="s">
+        <v>100</v>
+      </c>
+      <c r="G15" s="48" t="s">
+        <v>44</v>
+      </c>
+      <c r="H15" s="49" t="s">
+        <v>84</v>
+      </c>
+      <c r="I15" s="43">
+        <v>45958</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="26"/>
+      <c r="A16" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="43">
+        <v>45952</v>
+      </c>
+      <c r="C16" s="43">
+        <v>45958</v>
+      </c>
+      <c r="D16" s="51">
+        <v>135056992</v>
+      </c>
+      <c r="E16" s="18">
+        <v>3450117275</v>
+      </c>
+      <c r="F16" s="50" t="s">
+        <v>101</v>
+      </c>
+      <c r="G16" s="48" t="s">
+        <v>11</v>
+      </c>
+      <c r="H16" s="49" t="s">
+        <v>12</v>
+      </c>
+      <c r="I16" s="43">
+        <v>45957</v>
+      </c>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="26"/>
+      <c r="A17" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="43">
+        <v>45952</v>
+      </c>
+      <c r="C17" s="43">
+        <v>45958</v>
+      </c>
+      <c r="D17" s="51">
+        <v>135067409</v>
+      </c>
+      <c r="E17" s="18">
+        <v>3450117704</v>
+      </c>
+      <c r="F17" s="50" t="s">
+        <v>102</v>
+      </c>
+      <c r="G17" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="H17" s="49" t="s">
+        <v>103</v>
+      </c>
+      <c r="I17" s="43">
+        <v>45952</v>
+      </c>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="6"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="27"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="26"/>
+      <c r="A18" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="43">
+        <v>45974</v>
+      </c>
+      <c r="C18" s="43">
+        <v>45958</v>
+      </c>
+      <c r="D18" s="51">
+        <v>134945001</v>
+      </c>
+      <c r="E18" s="18">
+        <v>3450107650</v>
+      </c>
+      <c r="F18" s="50" t="s">
+        <v>104</v>
+      </c>
+      <c r="G18" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18" s="49" t="s">
+        <v>15</v>
+      </c>
+      <c r="I18" s="43">
+        <v>45974</v>
+      </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="6"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="26"/>
+      <c r="A19" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="43">
+        <v>45953</v>
+      </c>
+      <c r="C19" s="43">
+        <v>45958</v>
+      </c>
+      <c r="D19" s="51">
+        <v>135078174</v>
+      </c>
+      <c r="E19" s="18">
+        <v>3450119024</v>
+      </c>
+      <c r="F19" s="50" t="s">
+        <v>105</v>
+      </c>
+      <c r="G19" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="H19" s="49" t="s">
+        <v>106</v>
+      </c>
+      <c r="I19" s="43">
+        <v>45953</v>
+      </c>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="6"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="27"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="26"/>
+      <c r="A20" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="43">
+        <v>45961</v>
+      </c>
+      <c r="C20" s="43">
+        <v>45958</v>
+      </c>
+      <c r="D20" s="51">
+        <v>135100764</v>
+      </c>
+      <c r="E20" s="18">
+        <v>3450121081</v>
+      </c>
+      <c r="F20" s="50" t="s">
+        <v>107</v>
+      </c>
+      <c r="G20" s="48" t="s">
+        <v>11</v>
+      </c>
+      <c r="H20" s="57" t="s">
+        <v>92</v>
+      </c>
+      <c r="I20" s="43">
+        <v>45957</v>
+      </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="6"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="27"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="26"/>
+      <c r="A21" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="43">
+        <v>45952</v>
+      </c>
+      <c r="C21" s="43">
+        <v>45958</v>
+      </c>
+      <c r="D21" s="51">
+        <v>135068300</v>
+      </c>
+      <c r="E21" s="18">
+        <v>3450117187</v>
+      </c>
+      <c r="F21" s="50" t="s">
+        <v>108</v>
+      </c>
+      <c r="G21" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="H21" s="49" t="s">
+        <v>109</v>
+      </c>
+      <c r="I21" s="43">
+        <v>45952</v>
+      </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="6"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="27"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="26"/>
+      <c r="A22" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="43">
+        <v>45957</v>
+      </c>
+      <c r="C22" s="43">
+        <v>45958</v>
+      </c>
+      <c r="D22" s="51">
+        <v>135111265</v>
+      </c>
+      <c r="E22" s="18">
+        <v>3450121653</v>
+      </c>
+      <c r="F22" s="50" t="s">
+        <v>110</v>
+      </c>
+      <c r="G22" s="48" t="s">
+        <v>11</v>
+      </c>
+      <c r="H22" s="49" t="s">
+        <v>92</v>
+      </c>
+      <c r="I22" s="43">
+        <v>45957</v>
+      </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="6"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="24"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="26"/>
+      <c r="A23" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="43">
+        <v>45976</v>
+      </c>
+      <c r="C23" s="43">
+        <v>45958</v>
+      </c>
+      <c r="D23" s="51">
+        <v>134969357</v>
+      </c>
+      <c r="E23" s="18">
+        <v>3450109840</v>
+      </c>
+      <c r="F23" s="50" t="s">
+        <v>111</v>
+      </c>
+      <c r="G23" s="48" t="s">
+        <v>11</v>
+      </c>
+      <c r="H23" s="49" t="s">
+        <v>12</v>
+      </c>
+      <c r="I23" s="43">
+        <v>45957</v>
+      </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="6"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="27"/>
-      <c r="D24" s="24"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="26"/>
+      <c r="A24" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="43">
+        <v>45954</v>
+      </c>
+      <c r="C24" s="43">
+        <v>45958</v>
+      </c>
+      <c r="D24" s="51">
+        <v>134940138</v>
+      </c>
+      <c r="E24" s="18">
+        <v>3450107991</v>
+      </c>
+      <c r="F24" s="50" t="s">
+        <v>112</v>
+      </c>
+      <c r="G24" s="48" t="s">
+        <v>44</v>
+      </c>
+      <c r="H24" s="57" t="s">
+        <v>84</v>
+      </c>
+      <c r="I24" s="43">
+        <v>45958</v>
+      </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="6"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="24"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="26"/>
+      <c r="A25" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="43">
+        <v>45951</v>
+      </c>
+      <c r="C25" s="43">
+        <v>45958</v>
+      </c>
+      <c r="D25" s="51">
+        <v>134940600</v>
+      </c>
+      <c r="E25" s="18">
+        <v>3450108002</v>
+      </c>
+      <c r="F25" s="50" t="s">
+        <v>113</v>
+      </c>
+      <c r="G25" s="48" t="s">
+        <v>44</v>
+      </c>
+      <c r="H25" s="49" t="s">
+        <v>90</v>
+      </c>
+      <c r="I25" s="43">
+        <v>45957</v>
+      </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="6"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="27"/>
-      <c r="D26" s="24"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="31"/>
-      <c r="I26" s="26"/>
+      <c r="A26" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="43">
+        <v>45956</v>
+      </c>
+      <c r="C26" s="43">
+        <v>45958</v>
+      </c>
+      <c r="D26" s="51">
+        <v>134942677</v>
+      </c>
+      <c r="E26" s="18">
+        <v>3450108101</v>
+      </c>
+      <c r="F26" s="50" t="s">
+        <v>114</v>
+      </c>
+      <c r="G26" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="H26" s="49" t="s">
+        <v>115</v>
+      </c>
+      <c r="I26" s="43">
+        <v>45958</v>
+      </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="6"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="27"/>
-      <c r="D27" s="24"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="26"/>
+      <c r="A27" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="43">
+        <v>45945</v>
+      </c>
+      <c r="C27" s="43">
+        <v>45958</v>
+      </c>
+      <c r="D27" s="51">
+        <v>134943358</v>
+      </c>
+      <c r="E27" s="18">
+        <v>3450108167</v>
+      </c>
+      <c r="F27" s="50" t="s">
+        <v>116</v>
+      </c>
+      <c r="G27" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="H27" s="49" t="s">
+        <v>117</v>
+      </c>
+      <c r="I27" s="43">
+        <v>45958</v>
+      </c>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="6"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="27"/>
-      <c r="D28" s="24"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="26"/>
+      <c r="A28" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="43">
+        <v>45960</v>
+      </c>
+      <c r="C28" s="43">
+        <v>45958</v>
+      </c>
+      <c r="D28" s="51">
+        <v>134943983</v>
+      </c>
+      <c r="E28" s="18">
+        <v>3450108211</v>
+      </c>
+      <c r="F28" s="50" t="s">
+        <v>118</v>
+      </c>
+      <c r="G28" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="H28" s="49" t="s">
+        <v>119</v>
+      </c>
+      <c r="I28" s="43">
+        <v>45958</v>
+      </c>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="6"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="24"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="26"/>
+      <c r="A29" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="43">
+        <v>45946</v>
+      </c>
+      <c r="C29" s="43">
+        <v>45958</v>
+      </c>
+      <c r="D29" s="51">
+        <v>134944838</v>
+      </c>
+      <c r="E29" s="18">
+        <v>3450108277</v>
+      </c>
+      <c r="F29" s="50" t="s">
+        <v>120</v>
+      </c>
+      <c r="G29" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="H29" s="49" t="s">
+        <v>87</v>
+      </c>
+      <c r="I29" s="43">
+        <v>45958</v>
+      </c>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="6"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="27"/>
-      <c r="D30" s="24"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="20"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="26"/>
+      <c r="A30" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="43">
+        <v>45955</v>
+      </c>
+      <c r="C30" s="43">
+        <v>45958</v>
+      </c>
+      <c r="D30" s="51">
+        <v>134944891</v>
+      </c>
+      <c r="E30" s="18">
+        <v>3450108299</v>
+      </c>
+      <c r="F30" s="50" t="s">
+        <v>121</v>
+      </c>
+      <c r="G30" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="H30" s="49" t="s">
+        <v>87</v>
+      </c>
+      <c r="I30" s="43">
+        <v>45958</v>
+      </c>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="6"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="27"/>
-      <c r="D31" s="24"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="20"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="26"/>
+      <c r="A31" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" s="43">
+        <v>45940</v>
+      </c>
+      <c r="C31" s="43">
+        <v>45958</v>
+      </c>
+      <c r="D31" s="51">
+        <v>134945877</v>
+      </c>
+      <c r="E31" s="18">
+        <v>3450108410</v>
+      </c>
+      <c r="F31" s="50" t="s">
+        <v>122</v>
+      </c>
+      <c r="G31" s="48" t="s">
+        <v>44</v>
+      </c>
+      <c r="H31" s="49" t="s">
+        <v>90</v>
+      </c>
+      <c r="I31" s="43">
+        <v>45958</v>
+      </c>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="6"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="27"/>
-      <c r="D32" s="24"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="20"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="26"/>
+      <c r="A32" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" s="43">
+        <v>45972</v>
+      </c>
+      <c r="C32" s="43">
+        <v>45958</v>
+      </c>
+      <c r="D32" s="51">
+        <v>134948611</v>
+      </c>
+      <c r="E32" s="18">
+        <v>3450108552</v>
+      </c>
+      <c r="F32" s="50" t="s">
+        <v>123</v>
+      </c>
+      <c r="G32" s="48" t="s">
+        <v>44</v>
+      </c>
+      <c r="H32" s="49" t="s">
+        <v>124</v>
+      </c>
+      <c r="I32" s="43">
+        <v>45958</v>
+      </c>
     </row>
     <row r="33" spans="1:9">
-      <c r="A33" s="6"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="27"/>
-      <c r="D33" s="24"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="20"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="26"/>
+      <c r="A33" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33" s="43">
+        <v>45939</v>
+      </c>
+      <c r="C33" s="43">
+        <v>45958</v>
+      </c>
+      <c r="D33" s="51">
+        <v>134949601</v>
+      </c>
+      <c r="E33" s="18">
+        <v>3450108585</v>
+      </c>
+      <c r="F33" s="50" t="s">
+        <v>125</v>
+      </c>
+      <c r="G33" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="H33" s="49" t="s">
+        <v>119</v>
+      </c>
+      <c r="I33" s="43">
+        <v>45958</v>
+      </c>
     </row>
     <row r="34" spans="1:9">
-      <c r="A34" s="6"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="22"/>
-      <c r="E34" s="22"/>
-      <c r="F34" s="15"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="26"/>
+      <c r="A34" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B34" s="43">
+        <v>45967</v>
+      </c>
+      <c r="C34" s="43">
+        <v>45958</v>
+      </c>
+      <c r="D34" s="51">
+        <v>134953644</v>
+      </c>
+      <c r="E34" s="18">
+        <v>3450108860</v>
+      </c>
+      <c r="F34" s="50" t="s">
+        <v>126</v>
+      </c>
+      <c r="G34" s="48" t="s">
+        <v>44</v>
+      </c>
+      <c r="H34" s="49" t="s">
+        <v>127</v>
+      </c>
+      <c r="I34" s="43">
+        <v>45958</v>
+      </c>
     </row>
     <row r="35" spans="1:9">
-      <c r="A35" s="6"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="26"/>
+      <c r="A35" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B35" s="58">
+        <v>45945</v>
+      </c>
+      <c r="C35" s="43">
+        <v>45958</v>
+      </c>
+      <c r="D35" s="51">
+        <v>134955203</v>
+      </c>
+      <c r="E35" s="18">
+        <v>3450108970</v>
+      </c>
+      <c r="F35" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="G35" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="H35" s="49" t="s">
+        <v>129</v>
+      </c>
+      <c r="I35" s="43">
+        <v>45945</v>
+      </c>
     </row>
     <row r="36" spans="1:9">
-      <c r="A36" s="6"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="9"/>
-      <c r="I36" s="26"/>
+      <c r="A36" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B36" s="43">
+        <v>45954</v>
+      </c>
+      <c r="C36" s="43">
+        <v>45958</v>
+      </c>
+      <c r="D36" s="51">
+        <v>134955467</v>
+      </c>
+      <c r="E36" s="18">
+        <v>3450109003</v>
+      </c>
+      <c r="F36" s="50" t="s">
+        <v>130</v>
+      </c>
+      <c r="G36" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="H36" s="49" t="s">
+        <v>87</v>
+      </c>
+      <c r="I36" s="43">
+        <v>45958</v>
+      </c>
     </row>
     <row r="37" spans="1:9">
-      <c r="A37" s="6"/>
-      <c r="B37" s="8"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="9"/>
-      <c r="I37"/>
+      <c r="A37" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B37" s="43">
+        <v>45968</v>
+      </c>
+      <c r="C37" s="43">
+        <v>45958</v>
+      </c>
+      <c r="D37" s="51">
+        <v>135042534</v>
+      </c>
+      <c r="E37" s="18">
+        <v>3450115735</v>
+      </c>
+      <c r="F37" s="50" t="s">
+        <v>131</v>
+      </c>
+      <c r="G37" s="48" t="s">
+        <v>44</v>
+      </c>
+      <c r="H37" s="49" t="s">
+        <v>132</v>
+      </c>
+      <c r="I37" s="43">
+        <v>45957</v>
+      </c>
     </row>
     <row r="38" spans="1:9">
-      <c r="A38" s="6"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="9"/>
-      <c r="I38"/>
+      <c r="A38" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B38" s="43">
+        <v>45953</v>
+      </c>
+      <c r="C38" s="43">
+        <v>45958</v>
+      </c>
+      <c r="D38" s="51">
+        <v>135069992</v>
+      </c>
+      <c r="E38" s="18">
+        <v>3450118320</v>
+      </c>
+      <c r="F38" s="50" t="s">
+        <v>133</v>
+      </c>
+      <c r="G38" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="H38" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="I38" s="43">
+        <v>45953</v>
+      </c>
     </row>
     <row r="39" spans="1:9">
-      <c r="A39" s="6"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="9"/>
-      <c r="I39"/>
+      <c r="A39" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B39" s="43">
+        <v>45947</v>
+      </c>
+      <c r="C39" s="43">
+        <v>45958</v>
+      </c>
+      <c r="D39" s="51">
+        <v>134981862</v>
+      </c>
+      <c r="E39" s="18">
+        <v>3450110642</v>
+      </c>
+      <c r="F39" s="50" t="s">
+        <v>135</v>
+      </c>
+      <c r="G39" s="48" t="s">
+        <v>11</v>
+      </c>
+      <c r="H39" s="49" t="s">
+        <v>92</v>
+      </c>
+      <c r="I39" s="43">
+        <v>45957</v>
+      </c>
     </row>
     <row r="40" spans="1:9">
-      <c r="A40" s="6"/>
-      <c r="B40" s="8"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="9"/>
-      <c r="I40"/>
+      <c r="A40" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B40" s="43">
+        <v>45952</v>
+      </c>
+      <c r="C40" s="43">
+        <v>45958</v>
+      </c>
+      <c r="D40" s="51">
+        <v>135057013</v>
+      </c>
+      <c r="E40" s="18">
+        <v>3450117286</v>
+      </c>
+      <c r="F40" s="50" t="s">
+        <v>136</v>
+      </c>
+      <c r="G40" s="48" t="s">
+        <v>11</v>
+      </c>
+      <c r="H40" s="49" t="s">
+        <v>92</v>
+      </c>
+      <c r="I40" s="43">
+        <v>45957</v>
+      </c>
     </row>
     <row r="41" spans="1:9">
-      <c r="A41" s="6"/>
-      <c r="B41" s="8"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="6"/>
-      <c r="H41" s="9"/>
-      <c r="I41"/>
+      <c r="A41" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B41" s="43">
+        <v>45950</v>
+      </c>
+      <c r="C41" s="43">
+        <v>45958</v>
+      </c>
+      <c r="D41" s="51">
+        <v>135014593</v>
+      </c>
+      <c r="E41" s="18">
+        <v>3450113425</v>
+      </c>
+      <c r="F41" s="50" t="s">
+        <v>137</v>
+      </c>
+      <c r="G41" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="H41" s="49" t="s">
+        <v>15</v>
+      </c>
+      <c r="I41" s="43">
+        <v>45950</v>
+      </c>
     </row>
     <row r="42" spans="1:9">
-      <c r="A42" s="6"/>
-      <c r="B42" s="8"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="9"/>
-      <c r="I42"/>
+      <c r="A42" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B42" s="43">
+        <v>45950</v>
+      </c>
+      <c r="C42" s="43">
+        <v>45958</v>
+      </c>
+      <c r="D42" s="51">
+        <v>135018905</v>
+      </c>
+      <c r="E42" s="18">
+        <v>3450113799</v>
+      </c>
+      <c r="F42" s="50" t="s">
+        <v>138</v>
+      </c>
+      <c r="G42" s="61" t="s">
+        <v>14</v>
+      </c>
+      <c r="H42" s="49" t="s">
+        <v>15</v>
+      </c>
+      <c r="I42" s="43">
+        <v>45950</v>
+      </c>
     </row>
     <row r="43" spans="1:9">
-      <c r="A43" s="6"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="9"/>
-      <c r="I43"/>
+      <c r="A43" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B43" s="43">
+        <v>45958</v>
+      </c>
+      <c r="C43" s="43">
+        <v>45958</v>
+      </c>
+      <c r="D43" s="51">
+        <v>135132162</v>
+      </c>
+      <c r="E43" s="18">
+        <v>3450123556</v>
+      </c>
+      <c r="F43" s="62" t="s">
+        <v>139</v>
+      </c>
+      <c r="G43" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="H43" s="63" t="s">
+        <v>36</v>
+      </c>
+      <c r="I43" s="43">
+        <v>45958</v>
+      </c>
     </row>
     <row r="44" spans="1:9">
-      <c r="A44" s="6"/>
-      <c r="B44" s="8"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="6"/>
-      <c r="H44" s="9"/>
-      <c r="I44"/>
+      <c r="G44" s="59"/>
     </row>
     <row r="45" spans="1:9">
-      <c r="A45" s="6"/>
-      <c r="B45" s="8"/>
-      <c r="C45" s="7"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="6"/>
-      <c r="H45" s="9"/>
-      <c r="I45"/>
+      <c r="G45" s="60"/>
     </row>
     <row r="46" spans="1:9">
-      <c r="A46" s="6"/>
-      <c r="B46" s="8"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="9"/>
-      <c r="G46" s="6"/>
-      <c r="H46" s="9"/>
-      <c r="I46"/>
-    </row>
-    <row r="47" spans="1:9">
-      <c r="A47" s="6"/>
-      <c r="B47" s="8"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="9"/>
-      <c r="G47" s="6"/>
-      <c r="H47" s="9"/>
-      <c r="I47"/>
-    </row>
-    <row r="48" spans="1:9">
-      <c r="A48" s="6"/>
-      <c r="B48" s="8"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="9"/>
-      <c r="G48" s="6"/>
-      <c r="H48" s="9"/>
-      <c r="I48"/>
-    </row>
-    <row r="49" spans="1:9">
-      <c r="A49" s="6"/>
-      <c r="B49" s="8"/>
-      <c r="C49" s="7"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
-      <c r="F49" s="9"/>
-      <c r="G49" s="6"/>
-      <c r="H49" s="9"/>
-      <c r="I49"/>
-    </row>
-    <row r="50" spans="1:9">
-      <c r="A50" s="6"/>
-      <c r="B50" s="8"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="9"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="9"/>
-      <c r="I50"/>
-    </row>
-    <row r="51" spans="1:9">
-      <c r="A51" s="6"/>
-      <c r="B51" s="8"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="8"/>
-      <c r="E51" s="8"/>
-      <c r="F51" s="9"/>
-      <c r="G51" s="6"/>
-      <c r="H51" s="9"/>
-      <c r="I51"/>
-    </row>
-    <row r="52" spans="1:9">
-      <c r="A52" s="6"/>
-      <c r="B52" s="8"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="9"/>
-      <c r="G52" s="6"/>
-      <c r="H52" s="9"/>
-      <c r="I52"/>
-    </row>
-    <row r="53" spans="1:9">
-      <c r="A53" s="6"/>
-      <c r="B53" s="8"/>
-      <c r="C53" s="7"/>
-      <c r="D53" s="8"/>
-      <c r="E53" s="8"/>
-      <c r="F53" s="9"/>
-      <c r="G53" s="6"/>
-      <c r="H53" s="9"/>
-      <c r="I53"/>
-    </row>
-    <row r="54" spans="1:9">
-      <c r="A54" s="6"/>
-      <c r="B54" s="8"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="6"/>
-      <c r="H54" s="9"/>
-      <c r="I54"/>
-    </row>
-    <row r="55" spans="1:9">
-      <c r="A55" s="6"/>
-      <c r="B55" s="8"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="6"/>
-      <c r="H55" s="9"/>
-      <c r="I55"/>
+      <c r="G46" s="60"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="2">
+    <cfRule type="notContainsBlanks" priority="4">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A33" xr:uid="{4D257AA8-3FDB-42B7-A450-B3788B0ABB12}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A43" xr:uid="{4D257AA8-3FDB-42B7-A450-B3788B0ABB12}">
       <formula1>$J$2</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G41" xr:uid="{5FAA0C61-6912-46B8-8149-B719594B77CB}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G43" xr:uid="{5FAA0C61-6912-46B8-8149-B719594B77CB}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3069,8 +3944,8 @@
     <col min="5" max="5" width="17.85546875" style="17" customWidth="1"/>
     <col min="6" max="6" width="27" customWidth="1"/>
     <col min="7" max="7" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="31.5703125" customWidth="1"/>
-    <col min="9" max="9" width="21" style="26" customWidth="1"/>
+    <col min="8" max="8" width="33.85546875" customWidth="1"/>
+    <col min="9" max="9" width="21" style="25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -3098,53 +3973,67 @@
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="32" t="s">
+      <c r="I1" s="29" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="21"/>
+      <c r="A2" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="C2" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="D2" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="E2" s="18">
+        <v>3450124634</v>
+      </c>
+      <c r="F2" s="54" t="s">
+        <v>142</v>
+      </c>
+      <c r="G2" s="55" t="s">
+        <v>81</v>
+      </c>
+      <c r="H2" s="56" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="6"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="28"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="27"/>
       <c r="E3" s="18"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="12"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="13"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="6"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="28"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="27"/>
       <c r="E4" s="18"/>
       <c r="F4" s="12"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="12"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="32"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="6"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="28"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="27"/>
       <c r="E5" s="18"/>
       <c r="F5" s="12"/>
       <c r="G5" s="20"/>
@@ -3155,8 +4044,8 @@
         <v>9</v>
       </c>
       <c r="B6" s="6"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="28"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="27"/>
       <c r="E6" s="18"/>
       <c r="F6" s="12"/>
       <c r="G6" s="20"/>
@@ -3167,8 +4056,8 @@
         <v>9</v>
       </c>
       <c r="B7" s="6"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="28"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="27"/>
       <c r="E7" s="18"/>
       <c r="F7" s="12"/>
       <c r="G7" s="20"/>
@@ -3179,8 +4068,8 @@
         <v>9</v>
       </c>
       <c r="B8" s="6"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="28"/>
+      <c r="C8" s="26"/>
+      <c r="D8" s="27"/>
       <c r="E8" s="18"/>
       <c r="F8" s="12"/>
       <c r="G8" s="20"/>
@@ -3191,8 +4080,8 @@
         <v>9</v>
       </c>
       <c r="B9" s="6"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="28"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="27"/>
       <c r="E9" s="18"/>
       <c r="F9" s="12"/>
       <c r="G9" s="20"/>
@@ -3203,11 +4092,11 @@
         <v>9</v>
       </c>
       <c r="B10" s="6"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="24"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="23"/>
       <c r="E10" s="18"/>
       <c r="F10" s="12"/>
-      <c r="G10" s="23"/>
+      <c r="G10" s="22"/>
       <c r="H10" s="9"/>
     </row>
     <row r="11" spans="1:9">
@@ -3215,8 +4104,8 @@
         <v>9</v>
       </c>
       <c r="B11" s="6"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="28"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="27"/>
       <c r="E11" s="18"/>
       <c r="F11" s="12"/>
       <c r="G11" s="20"/>
@@ -3227,11 +4116,11 @@
         <v>9</v>
       </c>
       <c r="B12" s="6"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="24"/>
+      <c r="C12" s="26"/>
+      <c r="D12" s="23"/>
       <c r="E12" s="18"/>
       <c r="F12" s="12"/>
-      <c r="G12" s="23"/>
+      <c r="G12" s="22"/>
       <c r="H12" s="9"/>
     </row>
     <row r="13" spans="1:9">
@@ -3239,8 +4128,8 @@
         <v>9</v>
       </c>
       <c r="B13" s="6"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="28"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="27"/>
       <c r="E13" s="18"/>
       <c r="F13" s="12"/>
       <c r="G13" s="20"/>
@@ -3251,8 +4140,8 @@
         <v>9</v>
       </c>
       <c r="B14" s="6"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="28"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="27"/>
       <c r="E14" s="18"/>
       <c r="F14" s="12"/>
       <c r="G14" s="20"/>
@@ -3263,8 +4152,8 @@
         <v>9</v>
       </c>
       <c r="B15" s="6"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="28"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="27"/>
       <c r="E15" s="18"/>
       <c r="F15" s="12"/>
       <c r="G15" s="20"/>
@@ -3275,8 +4164,8 @@
         <v>9</v>
       </c>
       <c r="B16" s="6"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="28"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="27"/>
       <c r="E16" s="18"/>
       <c r="F16" s="12"/>
       <c r="G16" s="20"/>
@@ -3285,8 +4174,8 @@
     <row r="17" spans="1:8">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="28"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="27"/>
       <c r="E17" s="18"/>
       <c r="F17" s="12"/>
       <c r="G17" s="20"/>
@@ -3295,18 +4184,18 @@
     <row r="18" spans="1:8">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
-      <c r="C18" s="27"/>
-      <c r="D18" s="24"/>
+      <c r="C18" s="26"/>
+      <c r="D18" s="23"/>
       <c r="E18" s="18"/>
       <c r="F18" s="12"/>
-      <c r="G18" s="23"/>
+      <c r="G18" s="22"/>
       <c r="H18" s="9"/>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="6"/>
       <c r="B19" s="6"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="28"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="27"/>
       <c r="E19" s="18"/>
       <c r="F19" s="12"/>
       <c r="G19" s="20"/>
@@ -3315,8 +4204,8 @@
     <row r="20" spans="1:8">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
-      <c r="C20" s="27"/>
-      <c r="D20" s="28"/>
+      <c r="C20" s="26"/>
+      <c r="D20" s="27"/>
       <c r="E20" s="18"/>
       <c r="F20" s="12"/>
       <c r="G20" s="20"/>
@@ -3325,8 +4214,8 @@
     <row r="21" spans="1:8">
       <c r="A21" s="6"/>
       <c r="B21" s="7"/>
-      <c r="C21" s="27"/>
-      <c r="D21" s="28"/>
+      <c r="C21" s="26"/>
+      <c r="D21" s="27"/>
       <c r="E21" s="18"/>
       <c r="F21" s="12"/>
       <c r="G21" s="20"/>
@@ -3335,8 +4224,8 @@
     <row r="22" spans="1:8">
       <c r="A22" s="6"/>
       <c r="B22" s="7"/>
-      <c r="C22" s="27"/>
-      <c r="D22" s="28"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="27"/>
       <c r="E22" s="18"/>
       <c r="F22" s="12"/>
       <c r="G22" s="20"/>
@@ -3345,8 +4234,8 @@
     <row r="23" spans="1:8">
       <c r="A23" s="6"/>
       <c r="B23" s="7"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="28"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="27"/>
       <c r="E23" s="18"/>
       <c r="F23" s="12"/>
       <c r="G23" s="20"/>
@@ -3355,18 +4244,18 @@
     <row r="24" spans="1:8">
       <c r="A24" s="6"/>
       <c r="B24" s="7"/>
-      <c r="C24" s="27"/>
-      <c r="D24" s="24"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="23"/>
       <c r="E24" s="18"/>
       <c r="F24" s="12"/>
-      <c r="G24" s="23"/>
+      <c r="G24" s="22"/>
       <c r="H24" s="9"/>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="6"/>
       <c r="B25" s="7"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="28"/>
+      <c r="C25" s="26"/>
+      <c r="D25" s="27"/>
       <c r="E25" s="18"/>
       <c r="F25" s="12"/>
       <c r="G25" s="20"/>
@@ -3375,8 +4264,8 @@
     <row r="26" spans="1:8">
       <c r="A26" s="6"/>
       <c r="B26" s="7"/>
-      <c r="C26" s="27"/>
-      <c r="D26" s="28"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="27"/>
       <c r="E26" s="18"/>
       <c r="F26" s="12"/>
       <c r="G26" s="20"/>
@@ -3385,8 +4274,8 @@
     <row r="27" spans="1:8">
       <c r="A27" s="6"/>
       <c r="B27" s="7"/>
-      <c r="C27" s="27"/>
-      <c r="D27" s="28"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="27"/>
       <c r="E27" s="18"/>
       <c r="F27" s="12"/>
       <c r="G27" s="20"/>
@@ -3395,8 +4284,8 @@
     <row r="28" spans="1:8">
       <c r="A28" s="6"/>
       <c r="B28" s="7"/>
-      <c r="C28" s="27"/>
-      <c r="D28" s="28"/>
+      <c r="C28" s="26"/>
+      <c r="D28" s="27"/>
       <c r="E28" s="18"/>
       <c r="F28" s="12"/>
       <c r="G28" s="20"/>
@@ -3405,89 +4294,89 @@
     <row r="29" spans="1:8">
       <c r="A29" s="6"/>
       <c r="B29" s="7"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="24"/>
+      <c r="C29" s="26"/>
+      <c r="D29" s="23"/>
       <c r="E29" s="18"/>
       <c r="F29" s="12"/>
-      <c r="G29" s="23"/>
+      <c r="G29" s="22"/>
       <c r="H29" s="9"/>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="6"/>
       <c r="B30" s="7"/>
-      <c r="C30" s="27"/>
-      <c r="D30" s="24"/>
+      <c r="C30" s="26"/>
+      <c r="D30" s="23"/>
       <c r="E30" s="18"/>
       <c r="F30" s="12"/>
-      <c r="G30" s="23"/>
+      <c r="G30" s="22"/>
       <c r="H30" s="9"/>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="6"/>
       <c r="B31" s="7"/>
-      <c r="C31" s="27"/>
-      <c r="D31" s="24"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="23"/>
       <c r="E31" s="18"/>
       <c r="F31" s="12"/>
-      <c r="G31" s="23"/>
+      <c r="G31" s="22"/>
       <c r="H31" s="9"/>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="6"/>
       <c r="B32" s="7"/>
-      <c r="C32" s="27"/>
-      <c r="D32" s="24"/>
+      <c r="C32" s="26"/>
+      <c r="D32" s="23"/>
       <c r="E32" s="18"/>
       <c r="F32" s="12"/>
-      <c r="G32" s="23"/>
+      <c r="G32" s="22"/>
       <c r="H32" s="9"/>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="6"/>
       <c r="B33" s="7"/>
-      <c r="C33" s="27"/>
-      <c r="D33" s="24"/>
+      <c r="C33" s="26"/>
+      <c r="D33" s="23"/>
       <c r="E33" s="18"/>
       <c r="F33" s="12"/>
-      <c r="G33" s="23"/>
+      <c r="G33" s="22"/>
       <c r="H33" s="9"/>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="6"/>
       <c r="B34" s="7"/>
-      <c r="C34" s="27"/>
-      <c r="D34" s="24"/>
+      <c r="C34" s="26"/>
+      <c r="D34" s="23"/>
       <c r="E34" s="18"/>
       <c r="F34" s="12"/>
-      <c r="G34" s="23"/>
+      <c r="G34" s="22"/>
       <c r="H34" s="9"/>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="6"/>
       <c r="B35" s="7"/>
-      <c r="C35" s="27"/>
-      <c r="D35" s="24"/>
+      <c r="C35" s="26"/>
+      <c r="D35" s="23"/>
       <c r="E35" s="18"/>
       <c r="F35" s="12"/>
-      <c r="G35" s="23"/>
+      <c r="G35" s="22"/>
       <c r="H35" s="9"/>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="6"/>
       <c r="B36" s="7"/>
-      <c r="C36" s="27"/>
-      <c r="D36" s="24"/>
+      <c r="C36" s="26"/>
+      <c r="D36" s="23"/>
       <c r="E36" s="18"/>
       <c r="F36" s="12"/>
-      <c r="G36" s="23"/>
+      <c r="G36" s="22"/>
       <c r="H36" s="9"/>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="6"/>
       <c r="B37" s="8"/>
       <c r="C37" s="7"/>
-      <c r="D37" s="22"/>
-      <c r="E37" s="22"/>
+      <c r="D37" s="21"/>
+      <c r="E37" s="21"/>
       <c r="F37" s="15"/>
       <c r="G37" s="6"/>
       <c r="H37" s="9"/>
@@ -3625,12 +4514,12 @@
       </c>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
-      <c r="D2" s="28"/>
+      <c r="D2" s="27"/>
       <c r="E2" s="8"/>
       <c r="F2" s="12"/>
-      <c r="G2" s="29"/>
+      <c r="G2" s="28"/>
       <c r="H2" s="9"/>
-      <c r="I2" s="26"/>
+      <c r="I2" s="25"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
@@ -3638,12 +4527,12 @@
       </c>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
-      <c r="D3" s="28"/>
+      <c r="D3" s="27"/>
       <c r="E3" s="8"/>
       <c r="F3" s="12"/>
-      <c r="G3" s="29"/>
+      <c r="G3" s="28"/>
       <c r="H3" s="9"/>
-      <c r="I3" s="26"/>
+      <c r="I3" s="25"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
@@ -3651,12 +4540,12 @@
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
-      <c r="D4" s="28"/>
+      <c r="D4" s="27"/>
       <c r="E4" s="8"/>
       <c r="F4" s="12"/>
-      <c r="G4" s="29"/>
+      <c r="G4" s="28"/>
       <c r="H4" s="9"/>
-      <c r="I4" s="26"/>
+      <c r="I4" s="25"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
@@ -3664,12 +4553,12 @@
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
-      <c r="D5" s="28"/>
+      <c r="D5" s="27"/>
       <c r="E5" s="8"/>
       <c r="F5" s="12"/>
-      <c r="G5" s="29"/>
+      <c r="G5" s="28"/>
       <c r="H5" s="9"/>
-      <c r="I5" s="26"/>
+      <c r="I5" s="25"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
@@ -3677,12 +4566,12 @@
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
-      <c r="D6" s="28"/>
+      <c r="D6" s="27"/>
       <c r="E6" s="8"/>
       <c r="F6" s="12"/>
-      <c r="G6" s="29"/>
+      <c r="G6" s="28"/>
       <c r="H6" s="9"/>
-      <c r="I6" s="26"/>
+      <c r="I6" s="25"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
@@ -3690,12 +4579,12 @@
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
-      <c r="D7" s="28"/>
+      <c r="D7" s="27"/>
       <c r="E7" s="8"/>
       <c r="F7" s="12"/>
-      <c r="G7" s="29"/>
+      <c r="G7" s="28"/>
       <c r="H7" s="9"/>
-      <c r="I7" s="26"/>
+      <c r="I7" s="25"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
@@ -3703,12 +4592,12 @@
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
-      <c r="D8" s="28"/>
+      <c r="D8" s="27"/>
       <c r="E8" s="8"/>
       <c r="F8" s="12"/>
-      <c r="G8" s="29"/>
+      <c r="G8" s="28"/>
       <c r="H8" s="9"/>
-      <c r="I8" s="26"/>
+      <c r="I8" s="25"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
@@ -3716,12 +4605,12 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
-      <c r="D9" s="28"/>
+      <c r="D9" s="27"/>
       <c r="E9" s="8"/>
       <c r="F9" s="12"/>
-      <c r="G9" s="29"/>
+      <c r="G9" s="28"/>
       <c r="H9" s="9"/>
-      <c r="I9" s="26"/>
+      <c r="I9" s="25"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
@@ -3729,12 +4618,12 @@
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
-      <c r="D10" s="28"/>
+      <c r="D10" s="27"/>
       <c r="E10" s="8"/>
       <c r="F10" s="12"/>
-      <c r="G10" s="29"/>
+      <c r="G10" s="28"/>
       <c r="H10" s="9"/>
-      <c r="I10" s="26"/>
+      <c r="I10" s="25"/>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
@@ -3742,12 +4631,12 @@
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
-      <c r="D11" s="28"/>
+      <c r="D11" s="27"/>
       <c r="E11" s="8"/>
       <c r="F11" s="12"/>
-      <c r="G11" s="29"/>
+      <c r="G11" s="28"/>
       <c r="H11" s="9"/>
-      <c r="I11" s="26"/>
+      <c r="I11" s="25"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
@@ -3755,12 +4644,12 @@
       </c>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
-      <c r="D12" s="28"/>
+      <c r="D12" s="27"/>
       <c r="E12" s="8"/>
       <c r="F12" s="12"/>
-      <c r="G12" s="29"/>
+      <c r="G12" s="28"/>
       <c r="H12" s="9"/>
-      <c r="I12" s="26"/>
+      <c r="I12" s="25"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
@@ -3768,12 +4657,12 @@
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
-      <c r="D13" s="28"/>
+      <c r="D13" s="27"/>
       <c r="E13" s="8"/>
       <c r="F13" s="12"/>
-      <c r="G13" s="29"/>
+      <c r="G13" s="28"/>
       <c r="H13" s="9"/>
-      <c r="I13" s="26"/>
+      <c r="I13" s="25"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
@@ -3781,12 +4670,12 @@
       </c>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
-      <c r="D14" s="28"/>
+      <c r="D14" s="27"/>
       <c r="E14" s="8"/>
       <c r="F14" s="12"/>
-      <c r="G14" s="29"/>
+      <c r="G14" s="28"/>
       <c r="H14" s="9"/>
-      <c r="I14" s="26"/>
+      <c r="I14" s="25"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
@@ -3794,23 +4683,23 @@
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
-      <c r="D15" s="28"/>
+      <c r="D15" s="27"/>
       <c r="E15" s="8"/>
       <c r="F15" s="12"/>
-      <c r="G15" s="29"/>
+      <c r="G15" s="28"/>
       <c r="H15" s="9"/>
-      <c r="I15" s="26"/>
+      <c r="I15" s="25"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
-      <c r="D16" s="28"/>
+      <c r="D16" s="27"/>
       <c r="E16" s="8"/>
       <c r="F16" s="12"/>
-      <c r="G16" s="29"/>
+      <c r="G16" s="28"/>
       <c r="H16" s="9"/>
-      <c r="I16" s="26"/>
+      <c r="I16" s="25"/>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="6"/>
@@ -3821,7 +4710,7 @@
       <c r="F17" s="12"/>
       <c r="G17" s="6"/>
       <c r="H17" s="9"/>
-      <c r="I17" s="26"/>
+      <c r="I17" s="25"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6"/>
@@ -3832,7 +4721,7 @@
       <c r="F18" s="12"/>
       <c r="G18" s="6"/>
       <c r="H18" s="9"/>
-      <c r="I18" s="26"/>
+      <c r="I18" s="25"/>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6"/>
@@ -3843,7 +4732,7 @@
       <c r="F19" s="13"/>
       <c r="G19" s="6"/>
       <c r="H19" s="9"/>
-      <c r="I19" s="26"/>
+      <c r="I19" s="25"/>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6"/>
@@ -3854,7 +4743,7 @@
       <c r="F20" s="15"/>
       <c r="G20" s="6"/>
       <c r="H20" s="9"/>
-      <c r="I20" s="26"/>
+      <c r="I20" s="25"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6"/>
@@ -4273,63 +5162,63 @@
         <v>9</v>
       </c>
       <c r="B2" s="7"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="24"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="23"/>
       <c r="E2" s="18"/>
       <c r="F2" s="12"/>
       <c r="G2" s="20"/>
       <c r="H2" s="9"/>
-      <c r="I2" s="26"/>
+      <c r="I2" s="25"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="7"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="24"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="23"/>
       <c r="E3" s="18"/>
       <c r="F3" s="12"/>
       <c r="G3" s="20"/>
       <c r="H3" s="9"/>
-      <c r="I3" s="37"/>
+      <c r="I3" s="34"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="7"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="24"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="23"/>
       <c r="E4" s="18"/>
       <c r="F4" s="12"/>
       <c r="G4" s="20"/>
       <c r="H4" s="9"/>
-      <c r="I4" s="26"/>
+      <c r="I4" s="25"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="7"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="24"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="23"/>
       <c r="E5" s="18"/>
       <c r="F5" s="12"/>
       <c r="G5" s="20"/>
       <c r="H5" s="9"/>
-      <c r="I5" s="26"/>
+      <c r="I5" s="25"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6"/>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="35"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="32"/>
       <c r="G6" s="6"/>
       <c r="H6" s="9"/>
-      <c r="I6" s="26"/>
+      <c r="I6" s="25"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6"/>
@@ -4856,7 +5745,7 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="43" t="s">
+      <c r="H1" s="40" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="5" t="s">
@@ -4868,232 +5757,232 @@
         <v>9</v>
       </c>
       <c r="B2" s="7"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="24"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="23"/>
       <c r="E2" s="18"/>
       <c r="F2" s="19"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="26"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="25"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="7"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="24"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="23"/>
       <c r="E3" s="18"/>
       <c r="F3" s="19"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="26"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="25"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="7"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="24"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="23"/>
       <c r="E4" s="18"/>
       <c r="F4" s="19"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="26"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="25"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="7"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="24"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="23"/>
       <c r="E5" s="18"/>
       <c r="F5" s="19"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="39"/>
-      <c r="I5" s="26"/>
+      <c r="G5" s="38"/>
+      <c r="H5" s="36"/>
+      <c r="I5" s="25"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="7"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="24"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="23"/>
       <c r="E6" s="18"/>
       <c r="F6" s="19"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="26"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="37"/>
+      <c r="I6" s="25"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="7"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="24"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="23"/>
       <c r="E7" s="18"/>
       <c r="F7" s="19"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="40"/>
-      <c r="I7" s="26"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="37"/>
+      <c r="I7" s="25"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="7"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="24"/>
+      <c r="C8" s="26"/>
+      <c r="D8" s="23"/>
       <c r="E8" s="18"/>
       <c r="F8" s="19"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="40"/>
-      <c r="I8" s="26"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="37"/>
+      <c r="I8" s="25"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="7"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="24"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="23"/>
       <c r="E9" s="18"/>
       <c r="F9" s="19"/>
-      <c r="G9" s="45"/>
-      <c r="H9" s="38"/>
-      <c r="I9" s="26"/>
+      <c r="G9" s="42"/>
+      <c r="H9" s="35"/>
+      <c r="I9" s="25"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="7"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="24"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="23"/>
       <c r="E10" s="18"/>
       <c r="F10" s="19"/>
-      <c r="G10" s="45"/>
-      <c r="H10" s="38"/>
-      <c r="I10" s="26"/>
+      <c r="G10" s="42"/>
+      <c r="H10" s="35"/>
+      <c r="I10" s="25"/>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="7"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="24"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="23"/>
       <c r="E11" s="18"/>
       <c r="F11" s="19"/>
-      <c r="G11" s="45"/>
-      <c r="H11" s="38"/>
-      <c r="I11" s="26"/>
+      <c r="G11" s="42"/>
+      <c r="H11" s="35"/>
+      <c r="I11" s="25"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B12" s="7"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="24"/>
+      <c r="C12" s="26"/>
+      <c r="D12" s="23"/>
       <c r="E12" s="18"/>
       <c r="F12" s="19"/>
-      <c r="G12" s="45"/>
-      <c r="H12" s="38"/>
-      <c r="I12" s="26"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="35"/>
+      <c r="I12" s="25"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B13" s="7"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="24"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="23"/>
       <c r="E13" s="18"/>
       <c r="F13" s="19"/>
-      <c r="G13" s="45"/>
-      <c r="H13" s="38"/>
-      <c r="I13" s="26"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="35"/>
+      <c r="I13" s="25"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B14" s="7"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="24"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="23"/>
       <c r="E14" s="18"/>
       <c r="F14" s="19"/>
-      <c r="G14" s="45"/>
-      <c r="H14" s="38"/>
-      <c r="I14" s="26"/>
+      <c r="G14" s="42"/>
+      <c r="H14" s="35"/>
+      <c r="I14" s="25"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B15" s="7"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="24"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="23"/>
       <c r="E15" s="18"/>
       <c r="F15" s="19"/>
-      <c r="G15" s="45"/>
-      <c r="H15" s="38"/>
-      <c r="I15" s="26"/>
+      <c r="G15" s="42"/>
+      <c r="H15" s="35"/>
+      <c r="I15" s="25"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B16" s="7"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="24"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="23"/>
       <c r="E16" s="18"/>
       <c r="F16" s="12"/>
-      <c r="G16" s="45"/>
-      <c r="H16" s="38"/>
-      <c r="I16" s="26"/>
+      <c r="G16" s="42"/>
+      <c r="H16" s="35"/>
+      <c r="I16" s="25"/>
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1">
-      <c r="A17" s="29" t="s">
+      <c r="A17" s="28" t="s">
         <v>9</v>
       </c>
       <c r="B17" s="7"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="24"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="23"/>
       <c r="E17" s="18"/>
       <c r="F17" s="12"/>
-      <c r="G17" s="41"/>
-      <c r="H17" s="38"/>
-      <c r="I17" s="26"/>
+      <c r="G17" s="38"/>
+      <c r="H17" s="35"/>
+      <c r="I17" s="25"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B18" s="7"/>
-      <c r="C18" s="27"/>
-      <c r="D18" s="24"/>
+      <c r="C18" s="26"/>
+      <c r="D18" s="23"/>
       <c r="E18" s="18"/>
       <c r="F18" s="12"/>
-      <c r="G18" s="45"/>
-      <c r="H18" s="38"/>
-      <c r="I18" s="26"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="35"/>
+      <c r="I18" s="25"/>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6"/>
       <c r="B19" s="8"/>
       <c r="C19" s="7"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="36"/>
-      <c r="G19" s="33"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="31"/>
+      <c r="F19" s="33"/>
+      <c r="G19" s="30"/>
       <c r="H19" s="9"/>
-      <c r="I19" s="26"/>
+      <c r="I19" s="25"/>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6"/>
@@ -5102,9 +5991,9 @@
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
       <c r="F20" s="15"/>
-      <c r="G20" s="33"/>
+      <c r="G20" s="30"/>
       <c r="H20" s="9"/>
-      <c r="I20" s="26"/>
+      <c r="I20" s="25"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6"/>
@@ -5113,9 +6002,9 @@
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
       <c r="F21" s="9"/>
-      <c r="G21" s="33"/>
+      <c r="G21" s="30"/>
       <c r="H21" s="9"/>
-      <c r="I21" s="26"/>
+      <c r="I21" s="25"/>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="6"/>
@@ -5124,9 +6013,9 @@
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
       <c r="F22" s="9"/>
-      <c r="G22" s="33"/>
+      <c r="G22" s="30"/>
       <c r="H22" s="9"/>
-      <c r="I22" s="26"/>
+      <c r="I22" s="25"/>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="6"/>
@@ -5135,9 +6024,9 @@
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
       <c r="F23" s="9"/>
-      <c r="G23" s="33"/>
+      <c r="G23" s="30"/>
       <c r="H23" s="9"/>
-      <c r="I23" s="26"/>
+      <c r="I23" s="25"/>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="6"/>
@@ -5146,9 +6035,9 @@
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
       <c r="F24" s="9"/>
-      <c r="G24" s="33"/>
+      <c r="G24" s="30"/>
       <c r="H24" s="9"/>
-      <c r="I24" s="26"/>
+      <c r="I24" s="25"/>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="6"/>
@@ -5159,7 +6048,7 @@
       <c r="F25" s="9"/>
       <c r="G25" s="6"/>
       <c r="H25" s="9"/>
-      <c r="I25" s="26"/>
+      <c r="I25" s="25"/>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="6"/>
@@ -5170,7 +6059,7 @@
       <c r="F26" s="9"/>
       <c r="G26" s="6"/>
       <c r="H26" s="9"/>
-      <c r="I26" s="26"/>
+      <c r="I26" s="25"/>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="6"/>
@@ -5181,7 +6070,7 @@
       <c r="F27" s="9"/>
       <c r="G27" s="6"/>
       <c r="H27" s="9"/>
-      <c r="I27" s="26"/>
+      <c r="I27" s="25"/>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="6"/>
@@ -5192,7 +6081,7 @@
       <c r="F28" s="9"/>
       <c r="G28" s="6"/>
       <c r="H28" s="9"/>
-      <c r="I28" s="26"/>
+      <c r="I28" s="25"/>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="6"/>
@@ -5203,7 +6092,7 @@
       <c r="F29" s="9"/>
       <c r="G29" s="6"/>
       <c r="H29" s="9"/>
-      <c r="I29" s="26"/>
+      <c r="I29" s="25"/>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="6"/>
@@ -5214,7 +6103,7 @@
       <c r="F30" s="9"/>
       <c r="G30" s="6"/>
       <c r="H30" s="9"/>
-      <c r="I30" s="26"/>
+      <c r="I30" s="25"/>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="6"/>
@@ -5225,7 +6114,7 @@
       <c r="F31" s="9"/>
       <c r="G31" s="6"/>
       <c r="H31" s="9"/>
-      <c r="I31" s="26"/>
+      <c r="I31" s="25"/>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="6"/>
@@ -5236,7 +6125,7 @@
       <c r="F32" s="9"/>
       <c r="G32" s="6"/>
       <c r="H32" s="9"/>
-      <c r="I32" s="26"/>
+      <c r="I32" s="25"/>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="6"/>
@@ -5247,7 +6136,7 @@
       <c r="F33" s="9"/>
       <c r="G33" s="6"/>
       <c r="H33" s="9"/>
-      <c r="I33" s="26"/>
+      <c r="I33" s="25"/>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="6"/>
@@ -5258,7 +6147,7 @@
       <c r="F34" s="9"/>
       <c r="G34" s="6"/>
       <c r="H34" s="9"/>
-      <c r="I34" s="26"/>
+      <c r="I34" s="25"/>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="6"/>
@@ -5269,7 +6158,7 @@
       <c r="F35" s="9"/>
       <c r="G35" s="6"/>
       <c r="H35" s="9"/>
-      <c r="I35" s="26"/>
+      <c r="I35" s="25"/>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="6"/>
@@ -6174,60 +7063,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-496608</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-496608</Url>
-      <Description>QAFFA7D2F2TC-2102087286-496608</Description>
-    </_dlc_DocIdUrl>
-    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </DossierOwner>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ccca9d190a3c43e89f73773ee806c8b5>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ia4b831ccad64069ad2e0cbd870e9b8a>
-    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </alteradopor>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="44" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ac14f8cb44178d381f4c0afb30680a90">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5e58414b065c9b590c40efa77cd84bb6" ns1:_="" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="44" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="82971b2e5ff54b9dc00805486a4d5c6f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8457adf3efc192365c2193e8d9b17f97" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
     <xsd:import namespace="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea"/>
     <xsd:import namespace="ea6c6725-5210-4d6a-93cc-4cf85111ac5e"/>
@@ -6276,12 +7113,12 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="http://schemas.microsoft.com/sharepoint/v3" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="23" nillable="true" ma:displayName="Unified Compliance Policy Properties" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
+    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="23" nillable="true" ma:displayName="Propriedades da Política de Conformidade Unificada" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="24" nillable="true" ma:displayName="Unified Compliance Policy UI Action" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
+    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="24" nillable="true" ma:displayName="Ação de IU da Política de Conformidade Unificada" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
@@ -6290,12 +7127,12 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_dlc_DocId" ma:index="8" nillable="true" ma:displayName="Document ID Value" ma:description="The value of the document ID assigned to this item." ma:indexed="true" ma:internalName="_dlc_DocId" ma:readOnly="true">
+    <xsd:element name="_dlc_DocId" ma:index="8" nillable="true" ma:displayName="Valor do ID do Documento" ma:description="O valor do ID do documento atribuído a este item." ma:indexed="true" ma:internalName="_dlc_DocId" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_dlc_DocIdUrl" ma:index="9" nillable="true" ma:displayName="Document ID" ma:description="Permanent link to this document." ma:hidden="true" ma:internalName="_dlc_DocIdUrl" ma:readOnly="true">
+    <xsd:element name="_dlc_DocIdUrl" ma:index="9" nillable="true" ma:displayName="ID do Documento" ma:description="Ligação permanente a este documento." ma:hidden="true" ma:internalName="_dlc_DocIdUrl" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:URL">
@@ -6378,7 +7215,7 @@
         <xsd:restriction base="dms:DateTime"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Partilhado Com" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -6397,7 +7234,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Detalhes de Partilhado Com" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -6430,7 +7267,7 @@
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="26" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="10820af1-e82f-496e-bbcb-d9502914b7b2" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="26" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de Imagem" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="10820af1-e82f-496e-bbcb-d9502914b7b2" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -6513,8 +7350,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de Conteúdo"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -6603,6 +7440,58 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-496608</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-496608</Url>
+      <Description>QAFFA7D2F2TC-2102087286-496608</Description>
+    </_dlc_DocIdUrl>
+    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </DossierOwner>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ccca9d190a3c43e89f73773ee806c8b5>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ia4b831ccad64069ad2e0cbd870e9b8a>
+    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </alteradopor>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
@@ -6654,7 +7543,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77C4FEBA-AA82-4A7D-9425-A8C21D89CA15}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6662,7 +7551,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59B298F1-28E2-4CD2-8867-13645E3177BB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
